--- a/outputs/414-20.xlsx
+++ b/outputs/414-20.xlsx
@@ -98,8 +98,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -292,14 +296,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A4"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.57"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
     </row>

--- a/outputs/414-20.xlsx
+++ b/outputs/414-20.xlsx
@@ -296,14 +296,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.57"/>
   </cols>
   <sheetData>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
